--- a/features/quotation/data/MASTER_RATES.xlsx
+++ b/features/quotation/data/MASTER_RATES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHAKH NAIR\Desktop\Work\VIKRAM\features\quotation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DCE8E3-0E1F-4090-B95F-AEC604C91E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABF7F60-FA87-40DD-9F5E-901302C0FEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B27EDA18-C4A4-44CA-9B7D-115C474DD462}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B27EDA18-C4A4-44CA-9B7D-115C474DD462}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER" sheetId="1" r:id="rId1"/>
@@ -2193,21 +2193,21 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:L583"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="121.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="121.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="7.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="7.109375" style="3" customWidth="1"/>
     <col min="8" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>64</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -4847,23 +4847,15 @@
       <c r="G88" s="4">
         <v>850</v>
       </c>
-      <c r="H88" s="4">
-        <v>900</v>
-      </c>
-      <c r="I88" s="4">
-        <v>1300</v>
-      </c>
-      <c r="J88" s="4">
-        <v>1500</v>
-      </c>
-      <c r="K88" s="4">
-        <v>3500</v>
-      </c>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
       <c r="L88" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -4885,23 +4877,15 @@
       <c r="G89" s="4">
         <v>850</v>
       </c>
-      <c r="H89" s="4">
-        <v>900</v>
-      </c>
-      <c r="I89" s="4">
-        <v>1300</v>
-      </c>
-      <c r="J89" s="4">
-        <v>1500</v>
-      </c>
-      <c r="K89" s="4">
-        <v>3500</v>
-      </c>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
       <c r="L89" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -4931,7 +4915,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -4961,7 +4945,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -4991,7 +4975,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -5021,7 +5005,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -5051,7 +5035,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -5081,7 +5065,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -5111,7 +5095,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -5141,7 +5125,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -5171,7 +5155,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -5209,7 +5193,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -5247,7 +5231,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -5285,7 +5269,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -5323,7 +5307,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -5361,7 +5345,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -5399,7 +5383,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -5437,7 +5421,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -5475,7 +5459,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -5513,7 +5497,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -5551,7 +5535,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -5581,7 +5565,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -5611,7 +5595,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -5641,7 +5625,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -5671,7 +5655,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -5701,7 +5685,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -5731,7 +5715,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -5761,7 +5745,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -5791,7 +5775,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -5821,7 +5805,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -5851,7 +5835,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -5881,7 +5865,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -5911,7 +5895,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -5941,7 +5925,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -5971,7 +5955,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -6001,7 +5985,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -6031,7 +6015,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -6061,7 +6045,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -6091,7 +6075,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -6121,7 +6105,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -6151,7 +6135,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -6179,7 +6163,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -6207,7 +6191,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -6235,7 +6219,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -6263,7 +6247,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -6291,7 +6275,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -6319,7 +6303,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -6347,7 +6331,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -6375,7 +6359,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -6403,7 +6387,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -6431,7 +6415,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -6459,7 +6443,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -6487,7 +6471,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -6515,7 +6499,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -6543,7 +6527,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -6571,7 +6555,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -6599,7 +6583,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -6627,7 +6611,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -6655,7 +6639,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -6683,7 +6667,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -6711,7 +6695,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -6739,7 +6723,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -6767,7 +6751,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -6795,7 +6779,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -6823,7 +6807,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -6851,7 +6835,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -6879,7 +6863,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -6907,7 +6891,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -6935,7 +6919,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -6963,7 +6947,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -6991,7 +6975,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -7019,7 +7003,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -7047,7 +7031,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -7075,7 +7059,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -7103,7 +7087,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -7131,7 +7115,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -7159,7 +7143,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -7187,7 +7171,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -7215,7 +7199,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -7243,7 +7227,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -7271,7 +7255,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -7299,7 +7283,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -7327,7 +7311,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -7355,7 +7339,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -7383,7 +7367,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -7411,7 +7395,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -7439,7 +7423,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -7467,7 +7451,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -7495,7 +7479,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -7523,7 +7507,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -7551,7 +7535,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -7579,7 +7563,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -7607,7 +7591,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -7635,7 +7619,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -7663,7 +7647,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -7691,7 +7675,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -7719,7 +7703,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -7747,7 +7731,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -7775,7 +7759,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -7803,7 +7787,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -7831,7 +7815,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -7859,7 +7843,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -7887,7 +7871,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -7915,7 +7899,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -7943,7 +7927,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -7971,7 +7955,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -7999,7 +7983,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -8027,7 +8011,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -8055,7 +8039,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -8083,7 +8067,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -8111,7 +8095,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -8139,7 +8123,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -8167,7 +8151,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -8195,7 +8179,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -8223,7 +8207,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -8251,7 +8235,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -8279,7 +8263,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -8307,7 +8291,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -8335,7 +8319,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -8363,7 +8347,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -8391,7 +8375,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -8419,7 +8403,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -8447,7 +8431,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -8475,7 +8459,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -8503,7 +8487,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -8531,7 +8515,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -8559,7 +8543,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -8587,7 +8571,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -8615,7 +8599,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -8643,7 +8627,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -8671,7 +8655,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -8699,7 +8683,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -8727,7 +8711,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -8755,7 +8739,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -8783,7 +8767,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -8811,7 +8795,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -8839,7 +8823,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -8867,7 +8851,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -8895,7 +8879,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -8923,7 +8907,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -8951,7 +8935,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -8979,7 +8963,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -9007,7 +8991,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -9035,7 +9019,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -9063,7 +9047,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -9091,7 +9075,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -9119,7 +9103,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -9147,7 +9131,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -9175,7 +9159,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -9203,7 +9187,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -9231,7 +9215,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -9259,7 +9243,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -9287,7 +9271,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -9315,7 +9299,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -9343,7 +9327,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -9371,7 +9355,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -9399,7 +9383,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>244</v>
       </c>
@@ -9427,7 +9411,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -9455,7 +9439,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -9483,7 +9467,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -9511,7 +9495,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -9539,7 +9523,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -9567,7 +9551,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -9595,7 +9579,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -9623,7 +9607,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -9651,7 +9635,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -9679,7 +9663,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -9707,7 +9691,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -9735,7 +9719,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -9763,7 +9747,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -9791,7 +9775,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -9819,7 +9803,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -9847,7 +9831,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -9875,7 +9859,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -9903,7 +9887,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -9931,7 +9915,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -9959,7 +9943,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -9987,7 +9971,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -10015,7 +9999,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -10043,7 +10027,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -10071,7 +10055,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -10099,7 +10083,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -10127,7 +10111,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -10155,7 +10139,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -10183,7 +10167,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -10211,7 +10195,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -10239,7 +10223,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -10267,7 +10251,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -10295,7 +10279,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -10323,7 +10307,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -10351,7 +10335,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -10379,7 +10363,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -10407,7 +10391,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -10435,7 +10419,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -10463,7 +10447,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -10491,7 +10475,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -10519,7 +10503,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -10547,7 +10531,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -10575,7 +10559,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -10603,7 +10587,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -10631,7 +10615,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -10659,7 +10643,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -10687,7 +10671,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -10715,7 +10699,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -10743,7 +10727,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -10771,7 +10755,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -10799,7 +10783,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -10827,7 +10811,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -10855,7 +10839,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -10883,7 +10867,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -10911,7 +10895,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -10939,7 +10923,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -10967,7 +10951,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -10995,7 +10979,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -11023,7 +11007,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -11051,7 +11035,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -11079,7 +11063,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -11107,7 +11091,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -11135,7 +11119,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -11163,7 +11147,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -11191,7 +11175,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -11219,7 +11203,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -11247,7 +11231,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -11275,7 +11259,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -11303,7 +11287,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -11331,7 +11315,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -11359,7 +11343,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -11387,7 +11371,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -11415,7 +11399,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -11443,7 +11427,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -11471,7 +11455,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -11499,7 +11483,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -11527,7 +11511,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -11555,7 +11539,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -11583,7 +11567,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -11611,7 +11595,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -11639,7 +11623,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -11667,7 +11651,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -11695,7 +11679,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -11723,7 +11707,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -11751,7 +11735,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -11779,7 +11763,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -11807,7 +11791,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -11835,7 +11819,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -11863,7 +11847,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -11891,7 +11875,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -11919,7 +11903,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -11947,7 +11931,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -11975,7 +11959,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -12003,7 +11987,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -12031,7 +12015,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -12059,7 +12043,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -12087,7 +12071,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -12115,7 +12099,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -12143,7 +12127,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -12173,7 +12157,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -12203,7 +12187,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -12233,7 +12217,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -12263,7 +12247,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -12293,7 +12277,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -12327,7 +12311,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -12361,7 +12345,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -12395,7 +12379,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -12429,7 +12413,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -12463,7 +12447,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -12493,7 +12477,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -12523,7 +12507,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -12553,7 +12537,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -12583,7 +12567,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -12613,7 +12597,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -12643,7 +12627,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -12673,7 +12657,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -12703,7 +12687,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -12733,7 +12717,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -12763,7 +12747,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -12793,7 +12777,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -12823,7 +12807,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -12853,7 +12837,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -12883,7 +12867,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -12913,7 +12897,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -12943,7 +12927,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -12973,7 +12957,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -13003,7 +12987,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="371" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -13033,7 +13017,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -13063,7 +13047,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -13093,7 +13077,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -13123,7 +13107,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -13153,7 +13137,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -13183,7 +13167,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -13213,7 +13197,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -13243,7 +13227,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -13273,7 +13257,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="380" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -13303,7 +13287,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -13333,7 +13317,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -13363,7 +13347,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -13393,7 +13377,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -13423,7 +13407,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -13453,7 +13437,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -13483,7 +13467,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -13513,7 +13497,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -13543,7 +13527,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="389" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -13573,7 +13557,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="390" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -13603,7 +13587,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -13633,7 +13617,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -13663,7 +13647,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -13693,7 +13677,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -13723,7 +13707,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -13753,7 +13737,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -13783,7 +13767,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -13813,7 +13797,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -13843,7 +13827,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -13873,7 +13857,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -13903,7 +13887,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -13933,7 +13917,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -13963,7 +13947,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="403" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -13993,7 +13977,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="404" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -14023,7 +14007,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="405" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -14053,7 +14037,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -14083,7 +14067,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -14113,7 +14097,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -14143,7 +14127,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -14173,7 +14157,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -14203,7 +14187,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -14233,7 +14217,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -14263,7 +14247,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -14293,7 +14277,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -14323,7 +14307,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -14353,7 +14337,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -14383,7 +14367,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -14413,7 +14397,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -14443,7 +14427,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -14473,7 +14457,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -14503,7 +14487,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -14533,7 +14517,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="422" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -14563,7 +14547,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -14593,7 +14577,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -14623,7 +14607,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -14653,7 +14637,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -14683,7 +14667,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -14713,7 +14697,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -14743,7 +14727,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -14773,7 +14757,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -14803,7 +14787,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -14833,7 +14817,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="432" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -14863,7 +14847,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -14893,7 +14877,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -14923,7 +14907,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -14953,7 +14937,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -14983,7 +14967,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -15013,7 +14997,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A438" s="4">
         <v>437</v>
       </c>
@@ -15043,7 +15027,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A439" s="4">
         <v>438</v>
       </c>
@@ -15073,7 +15057,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A440" s="4">
         <v>439</v>
       </c>
@@ -15103,7 +15087,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A441" s="4">
         <v>440</v>
       </c>
@@ -15133,7 +15117,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A442" s="4">
         <v>441</v>
       </c>
@@ -15163,7 +15147,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A443" s="4">
         <v>442</v>
       </c>
@@ -15193,7 +15177,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A444" s="4">
         <v>443</v>
       </c>
@@ -15223,7 +15207,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A445" s="4">
         <v>444</v>
       </c>
@@ -15253,7 +15237,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A446" s="4">
         <v>445</v>
       </c>
@@ -15283,7 +15267,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A447" s="4">
         <v>446</v>
       </c>
@@ -15313,7 +15297,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A448" s="4">
         <v>447</v>
       </c>
@@ -15343,7 +15327,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A449" s="4">
         <v>448</v>
       </c>
@@ -15373,7 +15357,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A450" s="4">
         <v>449</v>
       </c>
@@ -15403,7 +15387,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A451" s="4">
         <v>450</v>
       </c>
@@ -15433,7 +15417,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A452" s="4">
         <v>451</v>
       </c>
@@ -15463,7 +15447,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A453" s="4">
         <v>452</v>
       </c>
@@ -15493,7 +15477,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A454" s="4">
         <v>453</v>
       </c>
@@ -15523,7 +15507,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A455" s="4">
         <v>454</v>
       </c>
@@ -15553,7 +15537,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A456" s="4">
         <v>455</v>
       </c>
@@ -15583,7 +15567,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
         <v>456</v>
       </c>
@@ -15613,7 +15597,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A458" s="4">
         <v>457</v>
       </c>
@@ -15643,7 +15627,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="459" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A459" s="4">
         <v>458</v>
       </c>
@@ -15673,7 +15657,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="460" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A460" s="4">
         <v>459</v>
       </c>
@@ -15703,7 +15687,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A461" s="4">
         <v>460</v>
       </c>
@@ -15733,7 +15717,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="462" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A462" s="4">
         <v>461</v>
       </c>
@@ -15763,7 +15747,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
         <v>462</v>
       </c>
@@ -15793,7 +15777,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="464" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
         <v>463</v>
       </c>
@@ -15823,7 +15807,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
         <v>464</v>
       </c>
@@ -15853,7 +15837,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
         <v>465</v>
       </c>
@@ -15883,7 +15867,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
         <v>466</v>
       </c>
@@ -15913,7 +15897,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A468" s="4">
         <v>467</v>
       </c>
@@ -15943,7 +15927,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="469" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
         <v>468</v>
       </c>
@@ -15973,7 +15957,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="470" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A470" s="4">
         <v>469</v>
       </c>
@@ -16003,7 +15987,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="471" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
         <v>470</v>
       </c>
@@ -16033,7 +16017,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="472" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A472" s="4">
         <v>471</v>
       </c>
@@ -16063,7 +16047,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="473" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A473" s="4">
         <v>472</v>
       </c>
@@ -16093,7 +16077,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="474" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A474" s="4">
         <v>473</v>
       </c>
@@ -16123,7 +16107,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="475" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A475" s="4">
         <v>474</v>
       </c>
@@ -16153,7 +16137,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="476" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A476" s="4">
         <v>475</v>
       </c>
@@ -16183,7 +16167,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="477" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
         <v>476</v>
       </c>
@@ -16213,7 +16197,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A478" s="4">
         <v>477</v>
       </c>
@@ -16243,7 +16227,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A479" s="4">
         <v>478</v>
       </c>
@@ -16273,7 +16257,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="480" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A480" s="4">
         <v>479</v>
       </c>
@@ -16303,7 +16287,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="481" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A481" s="4">
         <v>480</v>
       </c>
@@ -16333,7 +16317,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A482" s="4">
         <v>481</v>
       </c>
@@ -16363,7 +16347,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A483" s="4">
         <v>482</v>
       </c>
@@ -16393,7 +16377,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A484" s="4">
         <v>483</v>
       </c>
@@ -16423,7 +16407,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A485" s="4">
         <v>484</v>
       </c>
@@ -16453,7 +16437,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="486" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A486" s="4">
         <v>485</v>
       </c>
@@ -16483,7 +16467,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A487" s="4">
         <v>486</v>
       </c>
@@ -16513,7 +16497,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A488" s="4">
         <v>487</v>
       </c>
@@ -16543,7 +16527,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="489" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A489" s="4">
         <v>488</v>
       </c>
@@ -16573,7 +16557,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="490" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A490" s="4">
         <v>489</v>
       </c>
@@ -16603,7 +16587,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="491" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A491" s="4">
         <v>490</v>
       </c>
@@ -16633,7 +16617,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A492" s="4">
         <v>491</v>
       </c>
@@ -16663,7 +16647,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="493" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A493" s="4">
         <v>492</v>
       </c>
@@ -16693,7 +16677,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="494" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A494" s="4">
         <v>493</v>
       </c>
@@ -16723,7 +16707,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="495" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A495" s="4">
         <v>494</v>
       </c>
@@ -16753,7 +16737,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="496" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A496" s="4">
         <v>495</v>
       </c>
@@ -16783,7 +16767,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A497" s="4">
         <v>496</v>
       </c>
@@ -16813,7 +16797,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="498" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A498" s="4">
         <v>497</v>
       </c>
@@ -16843,7 +16827,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="499" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -16873,7 +16857,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="500" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A500" s="4">
         <v>499</v>
       </c>
@@ -16903,7 +16887,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="501" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A501" s="4">
         <v>500</v>
       </c>
@@ -16933,7 +16917,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="502" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A502" s="4">
         <v>501</v>
       </c>
@@ -16963,7 +16947,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="503" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A503" s="4">
         <v>502</v>
       </c>
@@ -16993,7 +16977,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="504" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A504" s="4">
         <v>503</v>
       </c>
@@ -17023,7 +17007,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="505" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A505" s="4">
         <v>504</v>
       </c>
@@ -17053,7 +17037,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="506" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A506" s="4">
         <v>505</v>
       </c>
@@ -17083,7 +17067,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="507" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A507" s="4">
         <v>506</v>
       </c>
@@ -17113,7 +17097,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="508" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A508" s="4">
         <v>507</v>
       </c>
@@ -17143,7 +17127,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="509" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A509" s="4">
         <v>508</v>
       </c>
@@ -17173,7 +17157,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A510" s="5"/>
       <c r="B510" s="5"/>
       <c r="C510" s="5"/>
@@ -17187,7 +17171,7 @@
       <c r="K510" s="4"/>
       <c r="L510" s="4"/>
     </row>
-    <row r="511" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A511" s="5"/>
       <c r="B511" s="5"/>
       <c r="C511" s="5"/>
@@ -17201,7 +17185,7 @@
       <c r="K511" s="4"/>
       <c r="L511" s="4"/>
     </row>
-    <row r="512" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A512" s="5"/>
       <c r="B512" s="5"/>
       <c r="C512" s="5"/>
@@ -17215,7 +17199,7 @@
       <c r="K512" s="4"/>
       <c r="L512" s="4"/>
     </row>
-    <row r="513" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A513" s="5"/>
       <c r="B513" s="5"/>
       <c r="C513" s="5"/>
@@ -17229,7 +17213,7 @@
       <c r="K513" s="4"/>
       <c r="L513" s="4"/>
     </row>
-    <row r="514" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A514" s="5"/>
       <c r="B514" s="5"/>
       <c r="C514" s="5"/>
@@ -17243,7 +17227,7 @@
       <c r="K514" s="4"/>
       <c r="L514" s="4"/>
     </row>
-    <row r="515" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A515" s="5"/>
       <c r="B515" s="5"/>
       <c r="C515" s="5"/>
@@ -17257,7 +17241,7 @@
       <c r="K515" s="4"/>
       <c r="L515" s="4"/>
     </row>
-    <row r="516" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A516" s="5"/>
       <c r="B516" s="5"/>
       <c r="C516" s="5"/>
@@ -17271,7 +17255,7 @@
       <c r="K516" s="4"/>
       <c r="L516" s="4"/>
     </row>
-    <row r="517" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A517" s="5"/>
       <c r="B517" s="5"/>
       <c r="C517" s="5"/>
@@ -17285,7 +17269,7 @@
       <c r="K517" s="4"/>
       <c r="L517" s="4"/>
     </row>
-    <row r="518" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A518" s="5"/>
       <c r="B518" s="5"/>
       <c r="C518" s="5"/>
@@ -17299,7 +17283,7 @@
       <c r="K518" s="4"/>
       <c r="L518" s="4"/>
     </row>
-    <row r="519" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A519" s="5"/>
       <c r="B519" s="5"/>
       <c r="C519" s="5"/>
@@ -17313,7 +17297,7 @@
       <c r="K519" s="4"/>
       <c r="L519" s="4"/>
     </row>
-    <row r="520" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A520" s="5"/>
       <c r="B520" s="5"/>
       <c r="C520" s="5"/>
@@ -17327,7 +17311,7 @@
       <c r="K520" s="4"/>
       <c r="L520" s="4"/>
     </row>
-    <row r="521" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A521" s="5"/>
       <c r="B521" s="5"/>
       <c r="C521" s="5"/>
@@ -17341,7 +17325,7 @@
       <c r="K521" s="4"/>
       <c r="L521" s="4"/>
     </row>
-    <row r="522" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A522" s="5"/>
       <c r="B522" s="5"/>
       <c r="C522" s="5"/>
@@ -17355,7 +17339,7 @@
       <c r="K522" s="4"/>
       <c r="L522" s="4"/>
     </row>
-    <row r="523" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A523" s="5"/>
       <c r="B523" s="5"/>
       <c r="C523" s="5"/>
@@ -17369,7 +17353,7 @@
       <c r="K523" s="4"/>
       <c r="L523" s="4"/>
     </row>
-    <row r="524" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A524" s="5"/>
       <c r="B524" s="5"/>
       <c r="C524" s="5"/>
@@ -17383,7 +17367,7 @@
       <c r="K524" s="4"/>
       <c r="L524" s="4"/>
     </row>
-    <row r="525" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A525" s="5"/>
       <c r="B525" s="5"/>
       <c r="C525" s="5"/>
@@ -17397,7 +17381,7 @@
       <c r="K525" s="4"/>
       <c r="L525" s="4"/>
     </row>
-    <row r="526" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A526" s="5"/>
       <c r="B526" s="5"/>
       <c r="C526" s="5"/>
@@ -17411,7 +17395,7 @@
       <c r="K526" s="4"/>
       <c r="L526" s="4"/>
     </row>
-    <row r="527" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A527" s="5"/>
       <c r="B527" s="5"/>
       <c r="C527" s="5"/>
@@ -17425,7 +17409,7 @@
       <c r="K527" s="4"/>
       <c r="L527" s="4"/>
     </row>
-    <row r="528" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A528" s="5"/>
       <c r="B528" s="5"/>
       <c r="C528" s="5"/>
@@ -17439,7 +17423,7 @@
       <c r="K528" s="4"/>
       <c r="L528" s="4"/>
     </row>
-    <row r="529" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A529" s="5"/>
       <c r="B529" s="5"/>
       <c r="C529" s="5"/>
@@ -17453,7 +17437,7 @@
       <c r="K529" s="4"/>
       <c r="L529" s="4"/>
     </row>
-    <row r="530" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A530" s="5"/>
       <c r="B530" s="5"/>
       <c r="C530" s="5"/>
@@ -17467,7 +17451,7 @@
       <c r="K530" s="4"/>
       <c r="L530" s="4"/>
     </row>
-    <row r="531" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A531" s="5"/>
       <c r="B531" s="5"/>
       <c r="C531" s="5"/>
@@ -17481,7 +17465,7 @@
       <c r="K531" s="4"/>
       <c r="L531" s="4"/>
     </row>
-    <row r="532" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A532" s="5"/>
       <c r="B532" s="5"/>
       <c r="C532" s="5"/>
@@ -17495,7 +17479,7 @@
       <c r="K532" s="4"/>
       <c r="L532" s="4"/>
     </row>
-    <row r="533" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A533" s="5"/>
       <c r="B533" s="5"/>
       <c r="C533" s="5"/>
@@ -17509,7 +17493,7 @@
       <c r="K533" s="4"/>
       <c r="L533" s="4"/>
     </row>
-    <row r="534" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A534" s="5"/>
       <c r="B534" s="5"/>
       <c r="C534" s="5"/>
@@ -17523,7 +17507,7 @@
       <c r="K534" s="4"/>
       <c r="L534" s="4"/>
     </row>
-    <row r="535" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A535" s="5"/>
       <c r="B535" s="5"/>
       <c r="C535" s="5"/>
@@ -17537,7 +17521,7 @@
       <c r="K535" s="4"/>
       <c r="L535" s="4"/>
     </row>
-    <row r="536" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A536" s="5"/>
       <c r="B536" s="5"/>
       <c r="C536" s="5"/>
@@ -17551,7 +17535,7 @@
       <c r="K536" s="4"/>
       <c r="L536" s="4"/>
     </row>
-    <row r="537" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A537" s="5"/>
       <c r="B537" s="5"/>
       <c r="C537" s="5"/>
@@ -17565,7 +17549,7 @@
       <c r="K537" s="4"/>
       <c r="L537" s="4"/>
     </row>
-    <row r="538" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A538" s="5"/>
       <c r="B538" s="5"/>
       <c r="C538" s="5"/>
@@ -17579,7 +17563,7 @@
       <c r="K538" s="4"/>
       <c r="L538" s="4"/>
     </row>
-    <row r="539" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A539" s="5"/>
       <c r="B539" s="5"/>
       <c r="C539" s="5"/>
@@ -17593,7 +17577,7 @@
       <c r="K539" s="4"/>
       <c r="L539" s="4"/>
     </row>
-    <row r="540" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A540" s="5"/>
       <c r="B540" s="5"/>
       <c r="C540" s="5"/>
@@ -17607,7 +17591,7 @@
       <c r="K540" s="4"/>
       <c r="L540" s="4"/>
     </row>
-    <row r="541" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A541" s="5"/>
       <c r="B541" s="5"/>
       <c r="C541" s="5"/>
@@ -17621,7 +17605,7 @@
       <c r="K541" s="4"/>
       <c r="L541" s="4"/>
     </row>
-    <row r="542" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A542" s="5"/>
       <c r="B542" s="5"/>
       <c r="C542" s="5"/>
@@ -17635,7 +17619,7 @@
       <c r="K542" s="4"/>
       <c r="L542" s="4"/>
     </row>
-    <row r="543" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A543" s="5"/>
       <c r="B543" s="5"/>
       <c r="C543" s="5"/>
@@ -17649,7 +17633,7 @@
       <c r="K543" s="4"/>
       <c r="L543" s="4"/>
     </row>
-    <row r="544" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A544" s="5"/>
       <c r="B544" s="5"/>
       <c r="C544" s="5"/>
@@ -17663,7 +17647,7 @@
       <c r="K544" s="4"/>
       <c r="L544" s="4"/>
     </row>
-    <row r="545" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A545" s="5"/>
       <c r="B545" s="5"/>
       <c r="C545" s="5"/>
@@ -17677,7 +17661,7 @@
       <c r="K545" s="4"/>
       <c r="L545" s="4"/>
     </row>
-    <row r="546" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A546" s="5"/>
       <c r="B546" s="5"/>
       <c r="C546" s="5"/>
@@ -17691,7 +17675,7 @@
       <c r="K546" s="4"/>
       <c r="L546" s="4"/>
     </row>
-    <row r="547" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A547" s="5"/>
       <c r="B547" s="5"/>
       <c r="C547" s="5"/>
@@ -17705,7 +17689,7 @@
       <c r="K547" s="4"/>
       <c r="L547" s="4"/>
     </row>
-    <row r="548" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A548" s="5"/>
       <c r="B548" s="5"/>
       <c r="C548" s="5"/>
@@ -17719,7 +17703,7 @@
       <c r="K548" s="4"/>
       <c r="L548" s="4"/>
     </row>
-    <row r="549" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A549" s="5"/>
       <c r="B549" s="5"/>
       <c r="C549" s="5"/>
@@ -17733,7 +17717,7 @@
       <c r="K549" s="4"/>
       <c r="L549" s="4"/>
     </row>
-    <row r="550" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A550" s="5"/>
       <c r="B550" s="5"/>
       <c r="C550" s="5"/>
@@ -17747,7 +17731,7 @@
       <c r="K550" s="4"/>
       <c r="L550" s="4"/>
     </row>
-    <row r="551" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A551" s="5"/>
       <c r="B551" s="5"/>
       <c r="C551" s="5"/>
@@ -17761,7 +17745,7 @@
       <c r="K551" s="4"/>
       <c r="L551" s="4"/>
     </row>
-    <row r="552" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A552" s="5"/>
       <c r="B552" s="5"/>
       <c r="C552" s="5"/>
@@ -17775,7 +17759,7 @@
       <c r="K552" s="4"/>
       <c r="L552" s="4"/>
     </row>
-    <row r="553" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A553" s="5"/>
       <c r="B553" s="5"/>
       <c r="C553" s="5"/>
@@ -17789,7 +17773,7 @@
       <c r="K553" s="4"/>
       <c r="L553" s="4"/>
     </row>
-    <row r="554" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A554" s="5"/>
       <c r="B554" s="5"/>
       <c r="C554" s="5"/>
@@ -17803,7 +17787,7 @@
       <c r="K554" s="4"/>
       <c r="L554" s="4"/>
     </row>
-    <row r="555" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A555" s="5"/>
       <c r="B555" s="5"/>
       <c r="C555" s="5"/>
@@ -17817,7 +17801,7 @@
       <c r="K555" s="4"/>
       <c r="L555" s="4"/>
     </row>
-    <row r="556" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A556" s="5"/>
       <c r="B556" s="5"/>
       <c r="C556" s="5"/>
@@ -17831,7 +17815,7 @@
       <c r="K556" s="4"/>
       <c r="L556" s="4"/>
     </row>
-    <row r="557" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A557" s="5"/>
       <c r="B557" s="5"/>
       <c r="C557" s="5"/>
@@ -17845,7 +17829,7 @@
       <c r="K557" s="4"/>
       <c r="L557" s="4"/>
     </row>
-    <row r="558" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A558" s="5"/>
       <c r="B558" s="5"/>
       <c r="C558" s="5"/>
@@ -17859,7 +17843,7 @@
       <c r="K558" s="4"/>
       <c r="L558" s="4"/>
     </row>
-    <row r="559" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A559" s="5"/>
       <c r="B559" s="5"/>
       <c r="C559" s="5"/>
@@ -17873,7 +17857,7 @@
       <c r="K559" s="4"/>
       <c r="L559" s="4"/>
     </row>
-    <row r="560" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A560" s="5"/>
       <c r="B560" s="5"/>
       <c r="C560" s="5"/>
@@ -17887,7 +17871,7 @@
       <c r="K560" s="4"/>
       <c r="L560" s="4"/>
     </row>
-    <row r="561" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A561" s="5"/>
       <c r="B561" s="5"/>
       <c r="C561" s="5"/>
@@ -17901,7 +17885,7 @@
       <c r="K561" s="4"/>
       <c r="L561" s="4"/>
     </row>
-    <row r="562" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A562" s="5"/>
       <c r="B562" s="5"/>
       <c r="C562" s="5"/>
@@ -17915,7 +17899,7 @@
       <c r="K562" s="4"/>
       <c r="L562" s="4"/>
     </row>
-    <row r="563" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A563" s="5"/>
       <c r="B563" s="5"/>
       <c r="C563" s="5"/>
@@ -17929,7 +17913,7 @@
       <c r="K563" s="4"/>
       <c r="L563" s="4"/>
     </row>
-    <row r="564" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A564" s="5"/>
       <c r="B564" s="5"/>
       <c r="C564" s="5"/>
@@ -17943,7 +17927,7 @@
       <c r="K564" s="4"/>
       <c r="L564" s="4"/>
     </row>
-    <row r="565" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A565" s="5"/>
       <c r="B565" s="5"/>
       <c r="C565" s="5"/>
@@ -17957,7 +17941,7 @@
       <c r="K565" s="4"/>
       <c r="L565" s="4"/>
     </row>
-    <row r="566" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A566" s="5"/>
       <c r="B566" s="5"/>
       <c r="C566" s="5"/>
@@ -17971,7 +17955,7 @@
       <c r="K566" s="4"/>
       <c r="L566" s="4"/>
     </row>
-    <row r="567" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A567" s="5"/>
       <c r="B567" s="5"/>
       <c r="C567" s="5"/>
@@ -17985,7 +17969,7 @@
       <c r="K567" s="4"/>
       <c r="L567" s="4"/>
     </row>
-    <row r="568" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A568" s="5"/>
       <c r="B568" s="5"/>
       <c r="C568" s="5"/>
@@ -17999,7 +17983,7 @@
       <c r="K568" s="4"/>
       <c r="L568" s="4"/>
     </row>
-    <row r="569" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A569" s="5"/>
       <c r="B569" s="5"/>
       <c r="C569" s="5"/>
@@ -18013,7 +17997,7 @@
       <c r="K569" s="4"/>
       <c r="L569" s="4"/>
     </row>
-    <row r="570" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A570" s="5"/>
       <c r="B570" s="5"/>
       <c r="C570" s="5"/>
@@ -18027,7 +18011,7 @@
       <c r="K570" s="4"/>
       <c r="L570" s="4"/>
     </row>
-    <row r="571" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A571" s="5"/>
       <c r="B571" s="5"/>
       <c r="C571" s="5"/>
@@ -18041,7 +18025,7 @@
       <c r="K571" s="4"/>
       <c r="L571" s="4"/>
     </row>
-    <row r="572" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A572" s="5"/>
       <c r="B572" s="5"/>
       <c r="C572" s="5"/>
@@ -18055,7 +18039,7 @@
       <c r="K572" s="4"/>
       <c r="L572" s="4"/>
     </row>
-    <row r="573" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A573" s="5"/>
       <c r="B573" s="5"/>
       <c r="C573" s="5"/>
@@ -18069,7 +18053,7 @@
       <c r="K573" s="4"/>
       <c r="L573" s="4"/>
     </row>
-    <row r="574" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A574" s="5"/>
       <c r="B574" s="5"/>
       <c r="C574" s="5"/>
@@ -18083,7 +18067,7 @@
       <c r="K574" s="4"/>
       <c r="L574" s="4"/>
     </row>
-    <row r="575" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A575" s="5"/>
       <c r="B575" s="5"/>
       <c r="C575" s="5"/>
@@ -18097,7 +18081,7 @@
       <c r="K575" s="4"/>
       <c r="L575" s="4"/>
     </row>
-    <row r="576" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A576" s="5"/>
       <c r="B576" s="5"/>
       <c r="C576" s="5"/>
@@ -18111,7 +18095,7 @@
       <c r="K576" s="4"/>
       <c r="L576" s="4"/>
     </row>
-    <row r="577" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A577" s="5"/>
       <c r="B577" s="5"/>
       <c r="C577" s="5"/>
@@ -18125,7 +18109,7 @@
       <c r="K577" s="4"/>
       <c r="L577" s="4"/>
     </row>
-    <row r="578" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A578" s="5"/>
       <c r="B578" s="5"/>
       <c r="C578" s="5"/>
@@ -18139,7 +18123,7 @@
       <c r="K578" s="4"/>
       <c r="L578" s="4"/>
     </row>
-    <row r="579" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A579" s="5"/>
       <c r="B579" s="5"/>
       <c r="C579" s="5"/>
@@ -18153,7 +18137,7 @@
       <c r="K579" s="4"/>
       <c r="L579" s="4"/>
     </row>
-    <row r="580" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A580" s="5"/>
       <c r="B580" s="5"/>
       <c r="C580" s="5"/>
@@ -18167,7 +18151,7 @@
       <c r="K580" s="4"/>
       <c r="L580" s="4"/>
     </row>
-    <row r="581" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A581" s="5"/>
       <c r="B581" s="5"/>
       <c r="C581" s="5"/>
@@ -18181,7 +18165,7 @@
       <c r="K581" s="4"/>
       <c r="L581" s="4"/>
     </row>
-    <row r="582" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A582" s="5"/>
       <c r="B582" s="5"/>
       <c r="C582" s="5"/>
@@ -18195,7 +18179,7 @@
       <c r="K582" s="4"/>
       <c r="L582" s="4"/>
     </row>
-    <row r="583" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A583" s="5"/>
       <c r="B583" s="5"/>
       <c r="C583" s="5"/>

--- a/features/quotation/data/MASTER_RATES.xlsx
+++ b/features/quotation/data/MASTER_RATES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHAKH NAIR\Desktop\Work\VIKRAM\features\quotation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABF7F60-FA87-40DD-9F5E-901302C0FEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29791EC7-E379-40CF-AA56-90F97171337C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B27EDA18-C4A4-44CA-9B7D-115C474DD462}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MASTER" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MASTER!$A$1:$L$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MASTER!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -18194,6 +18194,7 @@
       <c r="L583" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L1" xr:uid="{EBA4ACBF-9AD5-4FA6-903B-A6764EECAB0D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
